--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:27:21+00:00</t>
+          <t>2026-05-10T00:26:50+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:26:50+00:00</t>
+          <t>2026-05-11T00:27:13+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:13+00:00</t>
+          <t>2026-05-12T00:27:28+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:27:28+00:00</t>
+          <t>2026-05-13T00:29:52+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:29:52+00:00</t>
+          <t>2026-05-14T00:30:48+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:30:48+00:00</t>
+          <t>2026-05-15T00:28:35+00:00</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:28:35+00:00</t>
+          <t>2026-05-16T00:26:33+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,448 +717,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:26:33+00:00</t>
+          <t>2026-05-18T00:29:00+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -717,8 +717,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:00+00:00</t>
+          <t>2026-05-19T00:32:05+00:00</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:05+00:00</t>
+          <t>2026-05-20T00:33:40+00:00</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:33:40+00:00</t>
+          <t>2026-05-22T00:31:08+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -717,448 +717,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:31:08+00:00</t>
+          <t>2026-05-24T00:30:08+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,8 +717,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:30:08+00:00</t>
+          <t>2026-05-26T00:30:20+00:00</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:30:20+00:00</t>
+          <t>2026-05-28T00:29:37+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:29:37+00:00</t>
+          <t>2026-06-01T00:33:45+00:00</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31T08:11:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -603,7 +639,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -615,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,7 +661,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -637,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,7 +683,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -669,7 +705,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -691,7 +727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -713,7 +749,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -735,7 +771,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -757,7 +793,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -779,7 +815,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -801,7 +837,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -823,7 +859,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -835,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -845,7 +881,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -857,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -867,7 +903,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -879,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -889,7 +925,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -901,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -911,7 +947,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -923,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -933,7 +969,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -945,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -955,7 +991,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -977,7 +1013,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -999,7 +1035,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1057,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1079,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1101,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1087,7 +1123,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1145,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1131,7 +1167,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1153,7 +1189,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:33:45+00:00</t>
+          <t>2026-06-02T00:37:37+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -753,448 +753,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:37:37+00:00</t>
+          <t>2026-06-03T00:42:33+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -753,8 +753,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:42:33+00:00</t>
+          <t>2026-06-04T00:42:25+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-31T08:11:29+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -590,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -624,12 +588,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -639,19 +603,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -661,19 +625,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -683,19 +647,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -705,19 +669,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -727,19 +691,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -749,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -761,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -771,7 +735,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -783,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -793,7 +757,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -805,7 +769,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -815,7 +779,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -827,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -837,7 +801,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -849,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -859,7 +823,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -881,7 +845,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -903,7 +867,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -915,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -925,7 +889,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -947,7 +911,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -969,7 +933,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -991,7 +955,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1003,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1013,7 +977,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1025,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1035,7 +999,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1057,144 +1021,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:42:25+00:00</t>
+          <t>2026-06-07T00:34:08+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31T08:11:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -554,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,12 +624,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -603,19 +639,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,19 +661,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,19 +683,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -669,19 +705,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -691,19 +727,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>DPRK</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -713,7 +749,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -725,7 +761,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -735,7 +771,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -747,7 +783,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -757,7 +793,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -769,7 +805,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -779,7 +815,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -791,7 +827,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -801,7 +837,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -813,7 +849,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -823,7 +859,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -835,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -845,7 +881,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -857,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -867,7 +903,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -879,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -889,7 +925,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -901,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -911,7 +947,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -923,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -933,7 +969,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -945,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -955,7 +991,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -967,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -977,7 +1013,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -989,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -999,7 +1035,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1011,22 +1047,154 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>Syria</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:34:08+00:00</t>
+          <t>2026-06-08T00:35:45+00:00</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:35:45+00:00</t>
+          <t>2026-06-09T00:30:13+00:00</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:30:13+00:00</t>
+          <t>2026-06-10T00:36:28+00:00</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:36:28+00:00</t>
+          <t>2026-06-11T00:37:46+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-31T08:11:29+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -590,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -639,7 +603,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -651,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -661,7 +625,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -673,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -683,7 +647,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -705,7 +669,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -727,7 +691,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -749,452 +713,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:37:46+00:00</t>
+          <t>2026-06-12T00:38:32+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31T08:11:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -554,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -603,7 +639,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -625,7 +661,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -647,7 +683,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -669,7 +705,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -691,7 +727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -713,12 +749,452 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:38:32+00:00</t>
+          <t>2026-06-13T00:38:08+00:00</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:38:08+00:00</t>
+          <t>2026-06-14T00:35:58+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:35:58+00:00</t>
+          <t>2026-06-15T00:37:57+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:37:57+00:00</t>
+          <t>2026-06-16T00:43:12+00:00</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:43:12+00:00</t>
+          <t>2026-06-17T00:38:35+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:38:35+00:00</t>
+          <t>2026-06-18T00:39:24+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -753,448 +753,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:39:24+00:00</t>
+          <t>2026-06-19T00:42:35+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -753,8 +753,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:42:35+00:00</t>
+          <t>2026-06-20T00:33:40+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-31T08:11:29+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -590,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -624,132 +588,132 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -761,17 +725,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -783,17 +747,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -805,17 +769,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -827,17 +791,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -849,17 +813,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,17 +835,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,17 +857,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -915,17 +879,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,17 +901,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,17 +923,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,17 +945,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1003,17 +967,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1025,17 +989,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,154 +1011,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:33:40+00:00</t>
+          <t>2026-06-22T00:36:50+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31T08:11:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -554,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,132 +624,132 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>DPRK</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -725,17 +761,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -747,17 +783,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -769,17 +805,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -791,17 +827,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -813,17 +849,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -835,17 +871,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -857,17 +893,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -879,17 +915,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -901,17 +937,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -923,17 +959,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -945,17 +981,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -967,17 +1003,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -989,17 +1025,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -1011,22 +1047,154 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:36:50+00:00</t>
+          <t>2026-06-23T00:34:24+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23T00:34:24+00:00</t>
+          <t>2026-06-25T00:33:40+00:00</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:33:40+00:00</t>
+          <t>2026-06-26T00:34:46+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -624,12 +624,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -727,19 +727,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/Call-for-action-february-2026.html</t>
+          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1061,140 +1061,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26T00:34:46+00:00</t>
+          <t>2026-06-27T00:32:41+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-31T08:11:29+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -590,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -624,132 +588,132 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>DPRK</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -761,17 +725,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -783,17 +747,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -805,17 +769,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -827,17 +791,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -849,17 +813,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,17 +835,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,17 +857,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -915,17 +879,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,17 +901,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,17 +923,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,17 +945,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1003,17 +967,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1025,17 +989,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>February 2026</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,22 +1011,154 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260531081129/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-february-2026.html</t>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:32:41+00:00</t>
+          <t>2026-06-28T00:32:29+00:00</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:32:29+00:00</t>
+          <t>2026-06-29T00:33:55+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26T01:02:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -554,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,12 +624,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -603,19 +639,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,19 +661,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,19 +683,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -669,19 +705,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -691,19 +727,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -713,7 +749,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -725,7 +761,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -735,7 +771,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -747,7 +783,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -757,7 +793,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -769,7 +805,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -779,7 +815,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -791,7 +827,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -801,7 +837,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -813,7 +849,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -823,7 +859,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -835,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -845,7 +881,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -857,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -867,7 +903,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -879,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -889,7 +925,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -901,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -911,7 +947,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -923,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -933,7 +969,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -945,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -955,7 +991,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -967,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -977,7 +1013,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -989,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -999,7 +1035,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1021,144 +1057,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29T00:33:55+00:00</t>
+          <t>2026-06-30T00:33:07+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-26T01:02:34+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -590,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -624,12 +588,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -639,19 +603,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -661,19 +625,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -683,19 +647,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -705,19 +669,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -727,19 +691,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>DPRK</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -749,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -761,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -771,7 +735,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -783,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -793,7 +757,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -805,7 +769,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -815,7 +779,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -827,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -837,7 +801,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -849,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -859,7 +823,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -881,7 +845,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -903,7 +867,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -915,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -925,7 +889,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -947,7 +911,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -969,7 +933,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -991,7 +955,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1003,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1013,7 +977,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1025,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1035,7 +999,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,22 +1011,154 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
           <t>Namibia</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:33:07+00:00</t>
+          <t>2026-07-01T00:37:31+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -717,448 +717,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01T00:37:31+00:00</t>
+          <t>2026-07-02T00:33:10+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -717,8 +717,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02T00:33:10+00:00</t>
+          <t>2026-07-03T02:05:05+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:05:05+00:00</t>
+          <t>2026-07-04T02:02:08+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,448 +717,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04T02:02:08+00:00</t>
+          <t>2026-07-05T02:10:44+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,8 +717,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05T02:10:44+00:00</t>
+          <t>2026-07-06T02:15:33+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06T02:15:33+00:00</t>
+          <t>2026-07-07T02:11:03+00:00</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07T02:11:03+00:00</t>
+          <t>2026-07-08T01:51:52+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,448 +717,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08T01:51:52+00:00</t>
+          <t>2026-07-09T02:04:51+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26T01:02:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -554,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -603,7 +639,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -625,7 +661,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -647,7 +683,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -669,7 +705,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -691,7 +727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -713,12 +749,452 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09T02:04:51+00:00</t>
+          <t>2026-07-10T02:03:16+00:00</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10T02:03:16+00:00</t>
+          <t>2026-07-11T01:50:13+00:00</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26T01:02:34+00:00</t>
+          <t>2026-07-09T03:08:01+00:00</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260626010234/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11T01:50:13+00:00</t>
+          <t>2026-07-12T01:52:37+00:00</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:52:37+00:00</t>
+          <t>2026-07-13T01:55:25+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-09T03:08:01+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -590,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -624,12 +588,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -639,19 +603,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -661,19 +625,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -683,19 +647,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -705,19 +669,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -727,19 +691,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -749,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -761,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -771,7 +735,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -783,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -793,7 +757,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -805,7 +769,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -815,7 +779,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -827,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -837,7 +801,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -849,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -859,7 +823,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -881,7 +845,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -903,7 +867,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -915,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -925,7 +889,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -947,7 +911,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -969,7 +933,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -991,7 +955,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1003,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1013,7 +977,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1025,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1035,7 +999,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1057,144 +1021,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13T01:55:25+00:00</t>
+          <t>2026-07-14T01:42:30+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14T01:42:30+00:00</t>
+          <t>2026-07-15T01:28:20+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15T01:28:20+00:00</t>
+          <t>2026-07-16T01:48:49+00:00</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16T01:48:49+00:00</t>
+          <t>2026-07-17T01:52:14+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,12 +588,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -603,19 +603,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,19 +647,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -669,19 +669,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -691,19 +691,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>DPRK</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -713,320 +713,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17T01:52:14+00:00</t>
+          <t>2026-07-18T01:42:44+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09T03:08:01+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -554,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -603,7 +639,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -625,7 +661,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -647,7 +683,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -669,7 +705,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -691,7 +727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -713,12 +749,452 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18T01:42:44+00:00</t>
+          <t>2026-07-19T01:50:42+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19T01:50:42+00:00</t>
+          <t>2026-07-20T03:24:21+00:00</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20T03:24:21+00:00</t>
+          <t>2026-07-22T01:49:27+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22T01:49:27+00:00</t>
+          <t>2026-07-23T01:56:52+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -753,448 +753,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23T01:56:52+00:00</t>
+          <t>2026-07-24T01:52:26+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24T01:52:26+00:00</t>
+          <t>2026-07-25T01:52:20+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -753,8 +753,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25T01:52:20+00:00</t>
+          <t>2026-07-26T01:55:40+00:00</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26T01:55:40+00:00</t>
+          <t>2026-07-27T02:03:49+00:00</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27T02:03:49+00:00</t>
+          <t>2026-07-28T01:45:45+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28T01:45:45+00:00</t>
+          <t>2026-07-29T01:47:41+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29T01:47:41+00:00</t>
+          <t>2026-07-30T01:30:38+00:00</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30T01:30:38+00:00</t>
+          <t>2026-07-31T01:57:35+00:00</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31T01:57:35+00:00</t>
+          <t>2026-08-01T01:58:53+00:00</t>
         </is>
       </c>
     </row>
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-09T03:08:01+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -639,7 +603,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -661,7 +625,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -683,7 +647,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -705,7 +669,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -727,7 +691,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -749,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -771,7 +735,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -793,7 +757,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -815,7 +779,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -837,7 +801,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -859,7 +823,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -871,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -881,7 +845,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -893,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -903,7 +867,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -925,7 +889,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -937,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -947,7 +911,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -969,7 +933,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -991,7 +955,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1013,7 +977,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1035,7 +999,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1057,7 +1021,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1079,7 +1043,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1101,7 +1065,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1123,7 +1087,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1145,7 +1109,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1167,7 +1131,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1189,7 +1153,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01T01:58:53+00:00</t>
+          <t>2026-08-02T01:54:55+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T01:54:55+00:00</t>
+          <t>2026-08-03T01:57:35+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T01:57:35+00:00</t>
+          <t>2026-08-04T01:43:40+00:00</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,43 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>wayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot taken</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09T03:08:01+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Wayback snapshot URL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Staleness rule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Run fails if Wayback snapshot is older than 45 days</t>
         </is>
       </c>
     </row>
@@ -603,7 +639,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -615,7 +651,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,7 +661,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -637,7 +673,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,7 +683,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -669,7 +705,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -691,7 +727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -713,7 +749,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -735,7 +771,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -757,7 +793,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -779,7 +815,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -801,7 +837,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -823,7 +859,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -845,7 +881,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -867,7 +903,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -879,7 +915,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -889,7 +925,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -901,7 +937,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -911,7 +947,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -923,7 +959,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -933,7 +969,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -945,7 +981,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -955,7 +991,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -977,7 +1013,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -999,7 +1035,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1047,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1021,7 +1057,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1079,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1091,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1065,7 +1101,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1113,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1087,7 +1123,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1135,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1109,7 +1145,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1167,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1189,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T01:43:40+00:00</t>
+          <t>2026-08-05T01:45:36+00:00</t>
         </is>
       </c>
     </row>
@@ -533,43 +533,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>wayback</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot taken</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-09T03:08:01+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Wayback snapshot URL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Staleness rule</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Run fails if Wayback snapshot is older than 45 days</t>
+          <t>playwright</t>
         </is>
       </c>
     </row>
@@ -639,7 +603,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -651,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -661,7 +625,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -673,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -683,7 +647,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -705,7 +669,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -727,7 +691,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -749,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -771,7 +735,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -793,7 +757,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -815,7 +779,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -837,7 +801,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -859,7 +823,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -881,7 +845,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -903,7 +867,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -925,7 +889,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -947,7 +911,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -959,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -969,7 +933,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -981,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -991,7 +955,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1013,7 +977,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1035,7 +999,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1057,7 +1021,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1043,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1101,7 +1065,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1123,7 +1087,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1145,7 +1109,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1167,7 +1131,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1189,7 +1153,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260709030801/https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05T01:45:36+00:00</t>
+          <t>2026-08-06T01:45:58+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06T01:45:58+00:00</t>
+          <t>2026-08-07T02:10:25+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07T02:10:25+00:00</t>
+          <t>2026-08-08T00:57:31+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08T00:57:31+00:00</t>
+          <t>2026-08-09T01:00:57+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,448 +717,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09T01:00:57+00:00</t>
+          <t>2026-08-10T01:03:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10T01:03:11+00:00</t>
+          <t>2026-08-11T01:02:14+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,8 +717,448 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11T01:02:14+00:00</t>
+          <t>2026-08-12T01:09:23+00:00</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12T01:09:23+00:00</t>
+          <t>2026-08-13T01:11:27+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13T01:11:27+00:00</t>
+          <t>2026-08-14T01:10:08+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14T01:10:08+00:00</t>
+          <t>2026-08-15T00:43:07+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,12 +588,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -603,19 +603,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,19 +647,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -669,19 +669,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -691,19 +691,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1025,140 +1025,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15T00:43:07+00:00</t>
+          <t>2026-08-16T00:44:39+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,12 +588,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -603,19 +603,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,19 +647,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -669,19 +669,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -691,19 +691,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>DPRK</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,22 +1011,154 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>Namibia</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D21"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16T00:44:39+00:00</t>
+          <t>2026-08-17T00:42:47+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T00:42:47+00:00</t>
+          <t>2026-08-17T06:42:53+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:42:53+00:00</t>
+          <t>2026-08-17T07:42:42+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:42:42+00:00</t>
+          <t>2026-08-17T08:13:35+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:13:35+00:00</t>
+          <t>2026-08-17T08:28:50+00:00</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:28:50+00:00</t>
+          <t>2026-08-17T09:21:23+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -534,6 +534,18 @@
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Extraction</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>country-facet</t>
         </is>
       </c>
     </row>
@@ -554,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -593,7 +605,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of Korea</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,7 +627,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -632,12 +644,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -647,19 +659,19 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -669,19 +681,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -691,19 +703,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DPRK</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -713,7 +725,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -725,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -769,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -791,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -813,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -835,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -879,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -901,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -923,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -945,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -967,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -989,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1011,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1033,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1055,7 +1067,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1077,7 +1089,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Virgin Islands (UK)</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1113,52 +1125,8 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D27"/>
+  <autoFilter ref="A1:D25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:21:23+00:00</t>
+          <t>2026-08-17T09:26:50+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -644,12 +644,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1111,22 +1111,44 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
+          <t>Virgin Islands (UK)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:26:50+00:00</t>
+          <t>2026-08-17T10:45:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:45:29+00:00</t>
+          <t>2026-08-17T12:51:55+00:00</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:51:55+00:00</t>
+          <t>2026-08-17T23:14:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:14:23+00:00</t>
+          <t>2026-08-18T05:52:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:52:50+00:00</t>
+          <t>2026-08-19T23:15:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:15:14+00:00</t>
+          <t>2026-08-20T23:17:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:17:39+00:00</t>
+          <t>2026-08-21T23:15:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:04+00:00</t>
+          <t>2026-08-22T23:12:12+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -663,492 +663,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Lao PDR</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Syria</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Virgin Islands (UK)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:12:12+00:00</t>
+          <t>2026-08-23T23:12:28+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -663,8 +663,492 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Lao PDR</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Virgin Islands (UK)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:12:28+00:00</t>
+          <t>2026-08-24T23:15:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:15:39+00:00</t>
+          <t>2026-08-25T23:17:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:17:41+00:00</t>
+          <t>2026-08-27T04:09:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:09:33+00:00</t>
+          <t>2026-08-28T06:26:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:26:24+00:00</t>
+          <t>2026-08-29T03:58:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T03:58:41+00:00</t>
+          <t>2026-08-30T00:55:24+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of Korea</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,19 +615,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Virgin Islands (UK)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1081,74 +1081,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Virgin Islands (UK)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:55:24+00:00</t>
+          <t>2026-08-31T01:00:46+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Democratic Republic of Korea</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,19 +615,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,22 +1067,88 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Virgin Islands (UK)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:00:46+00:00</t>
+          <t>2026-09-01T01:31:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:31:25+00:00</t>
+          <t>2026-09-02T00:41:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:41:19+00:00</t>
+          <t>2026-09-03T00:52:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:52:59+00:00</t>
+          <t>2026-09-04T00:33:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:07+00:00</t>
+          <t>2026-09-05T00:29:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:29:22+00:00</t>
+          <t>2026-09-06T00:24:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:24:01+00:00</t>
+          <t>2026-09-07T00:30:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:30:58+00:00</t>
+          <t>2026-09-07T07:49:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:49:10+00:00</t>
+          <t>2026-09-07T09:42:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:42:44+00:00</t>
+          <t>2026-09-07T11:02:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:02:29+00:00</t>
+          <t>2026-09-08T00:49:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:49:41+00:00</t>
+          <t>2026-09-09T00:53:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:53:24+00:00</t>
+          <t>2026-09-09T01:45:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:45:02+00:00</t>
+          <t>2026-09-09T02:38:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:38:12+00:00</t>
+          <t>2026-09-10T00:43:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:43:49+00:00</t>
+          <t>2026-09-11T00:41:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:41:53+00:00</t>
+          <t>2026-09-12T00:49:10+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of Korea</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,19 +615,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Virgin Islands (UK)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1081,74 +1081,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Virgin Islands (UK)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:49:10+00:00</t>
+          <t>2026-09-13T00:30:40+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Democratic Republic of Korea</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,19 +615,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,22 +1067,88 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Virgin Islands (UK)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>